--- a/docs/test_report_document.xlsx
+++ b/docs/test_report_document.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="テスト計画概要" sheetId="1" state="visible" r:id="rId3"/>
@@ -27,21 +27,158 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="330">
-  <si>
-    <t xml:space="preserve">テスト報告書（Pet Life Plus）</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="331">
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">テスト報告書（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Pet Life Plus</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">テスト対象範囲</t>
   </si>
   <si>
-    <t xml:space="preserve">F-001〜F-021（認証・共通、ペット・健康管理、診療・予約、AI・チャット、カレンダー・通知、サブスク・パスワード、外部連携、管理・運営、共通制御）</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F-001</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F-021</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">（認証・共通、ペット・健康管理、診療・予約、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">・チャット、カレンダー・通知、サブスク・パスワード、外部連携、管理・運営、共通制御）</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">テスト種別</t>
   </si>
   <si>
-    <t xml:space="preserve">機能テスト / 画面テスト / セキュリティテスト</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">機能テスト </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">画面テスト </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">セキュリティテスト</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">テスト環境（ブラウザ）</t>
@@ -50,7 +187,36 @@
     <t xml:space="preserve">Chrome, Edge, Firefox, Safari(iOS)</t>
   </si>
   <si>
-    <t xml:space="preserve">テスト環境（OS）</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">テスト環境（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">OS</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">Windows 11, macOS 14, iOS 18, Android 15</t>
@@ -59,13 +225,161 @@
     <t xml:space="preserve">テスト期間</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-18 ～ 2026-06-29（予備日 2026-06-01）</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-05-18 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">～ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-06-29</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">（予備日 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-06-01</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">完了判定</t>
   </si>
   <si>
-    <t xml:space="preserve">重大不具合(高) 0件、実行率100%、合格率95%以上</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">重大不具合</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">高</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) 0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">件、実行率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">、合格率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">95%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">以上</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">ID</t>
@@ -86,7 +400,26 @@
     <t xml:space="preserve">TC-001</t>
   </si>
   <si>
-    <t xml:space="preserve">F-001 ログイン認証</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F-001 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ログイン認証</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">正常系</t>
@@ -98,6 +431,9 @@
     <t xml:space="preserve">認証成功しダッシュボードへ遷移する</t>
   </si>
   <si>
+    <t xml:space="preserve">OK</t>
+  </si>
+  <si>
     <t xml:space="preserve">TC-002</t>
   </si>
   <si>
@@ -107,7 +443,27 @@
     <t xml:space="preserve">パスワード誤りでログインする</t>
   </si>
   <si>
-    <t xml:space="preserve">認証エラーが表示されログイン不可</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">認証エラーが表示されログイン不可
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">メールアドレスまたはパスワードが正しくありません。</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">TC-003</t>
@@ -116,7 +472,27 @@
     <t xml:space="preserve">未登録メールでログインする</t>
   </si>
   <si>
-    <t xml:space="preserve">認証エラーが表示される</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">認証エラーが表示される
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">メールアドレスまたはパスワードが正しくありません。</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">TC-004</t>
@@ -125,7 +501,36 @@
     <t xml:space="preserve">セキュリティ</t>
   </si>
   <si>
-    <t xml:space="preserve">認証なしで /app/dashboard に直接アクセスする</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">認証なしで </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/app/dashboard </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">に直接アクセスする</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">ログイン画面にリダイレクトされる</t>
@@ -134,22 +539,147 @@
     <t xml:space="preserve">TC-005</t>
   </si>
   <si>
-    <t xml:space="preserve">F-002 ダッシュボード</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADMIN でログインしてダッシュボードを開く</t>
-  </si>
-  <si>
-    <t xml:space="preserve">管理系KPI（ユーザー数・予約数等）が表示される</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F-002 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ダッシュボード</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ADMIN </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">でログインしてダッシュボードを開く</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">管理系</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">KPI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">（ユーザー数・予約数等）が表示される</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">TC-006</t>
   </si>
   <si>
-    <t xml:space="preserve">一般ユーザー（Light）でログインしてダッシュボードを開く</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ユーザー系KPI（自ペット・予約・通知）が表示される</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">一般ユーザー（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Light</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">）でログインしてダッシュボードを開く</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ユーザー系</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">KPI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">（自ペット・予約・通知）が表示される</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">TC-007</t>
@@ -158,16 +688,83 @@
     <t xml:space="preserve">境界値</t>
   </si>
   <si>
-    <t xml:space="preserve">ペット・予約ともに0件の状態でダッシュボードを開く</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0件表示で画面崩れなく表示される</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ペット・予約ともに</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">件の状態でダッシュボードを開く</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">件表示で画面崩れなく表示される</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">TC-008</t>
   </si>
   <si>
-    <t xml:space="preserve">F-003 ユーザー管理</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F-003 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ユーザー管理</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">必須項目を入力してユーザー登録する</t>
@@ -182,13 +779,61 @@
     <t xml:space="preserve">既存メールアドレスで登録する</t>
   </si>
   <si>
-    <t xml:space="preserve">USR-001 重複エラーが表示され保存されない</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">USR-001 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">重複エラーが表示され保存されない</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">TC-010</t>
   </si>
   <si>
-    <t xml:space="preserve">一般ユーザーのプランを Standard に変更する</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">一般ユーザーのプランを </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Standard </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">に変更する</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">サブスクリプションが更新され一覧に反映される</t>
@@ -197,25 +842,160 @@
     <t xml:space="preserve">TC-011</t>
   </si>
   <si>
-    <t xml:space="preserve">LINE ID・Slack ID を登録して編集フォームの連携ステータスを確認する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LINE/Slack チップが色付きで表示される</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LINE ID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Slack ID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">を登録して編集フォームの連携ステータスを確認する</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LINE/Slack </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">チップが色付きで表示される</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">TC-012</t>
   </si>
   <si>
-    <t xml:space="preserve">LINE ID 未登録のユーザーの連携ステータスを確認する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LINE チップがグレー表示、ツールチップに「ID未登録」と表示される</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LINE ID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">未登録のユーザーの連携ステータスを確認する</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LINE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">チップがグレー表示、ツールチップに「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">未登録」と表示される</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">TC-013</t>
   </si>
   <si>
-    <t xml:space="preserve">VET ロールでユーザー編集フォームを開く</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">VET </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ロールでユーザー編集フォームを開く</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">編集・削除ボタンが表示されない（閲覧のみ）</t>
@@ -224,7 +1004,26 @@
     <t xml:space="preserve">TC-014</t>
   </si>
   <si>
-    <t xml:space="preserve">F-004 ペット管理</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F-004 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ペット管理</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">必須項目を入力してペットを登録する</t>
@@ -263,7 +1062,26 @@
     <t xml:space="preserve">TC-018</t>
   </si>
   <si>
-    <t xml:space="preserve">F-005 健康記録管理</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F-005 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">健康記録管理</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">記録日・体重を入力して登録する</t>
@@ -284,7 +1102,36 @@
     <t xml:space="preserve">TC-020</t>
   </si>
   <si>
-    <t xml:space="preserve">体重0.1 kg で登録する</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">体重</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.1 kg </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">で登録する</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">下限値として正常登録される</t>
@@ -293,28 +1140,162 @@
     <t xml:space="preserve">TC-021</t>
   </si>
   <si>
-    <t xml:space="preserve">F-006 診療予約</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Standard 以上のユーザーが未来日時で予約申請する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ステータス REQUESTED で保存される</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F-006 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">診療予約</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Standard </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">以上のユーザーが未来日時で予約申請する</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ステータス </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">REQUESTED </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">で保存される</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">TC-022</t>
   </si>
   <si>
-    <t xml:space="preserve">STAFF が申請中の予約を承認する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ステータスが CONFIRMED になりオーナーに通知が届く</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">STAFF </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">が申請中の予約を承認する</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ステータスが </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CONFIRMED </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">になりオーナーに通知が届く</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">TC-023</t>
   </si>
   <si>
-    <t xml:space="preserve">STAFF が承認後にカレンダーを開く</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">STAFF </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">が承認後にカレンダーを開く</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">承認済み予約が該当日に表示される</t>
@@ -323,10 +1304,58 @@
     <t xml:space="preserve">TC-024</t>
   </si>
   <si>
-    <t xml:space="preserve">STAFF が申請中の予約を却下する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ステータスが CANCELED になりオーナーに通知が届く</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">STAFF </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">が申請中の予約を却下する</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ステータスが </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CANCELED </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">になりオーナーに通知が届く</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">TC-025</t>
@@ -341,7 +1370,36 @@
     <t xml:space="preserve">TC-026</t>
   </si>
   <si>
-    <t xml:space="preserve">診療受付時間外（17:01）で申請する</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">診療受付時間外（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">17:01</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">）で申請する</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">「診療受付時間外」エラーが表示される</t>
@@ -350,7 +1408,46 @@
     <t xml:space="preserve">TC-027</t>
   </si>
   <si>
-    <t xml:space="preserve">ADMIN ロールで /app/appointments にアクセスする</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ADMIN </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ロールで </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/app/appointments </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">にアクセスする</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">アクセス拒否ページが表示される（設計通り）</t>
@@ -359,10 +1456,48 @@
     <t xml:space="preserve">TC-028</t>
   </si>
   <si>
-    <t xml:space="preserve">F-007 診療記録</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VET が実施日・対応内容を入力して診療記録を登録する</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F-007 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">診療記録</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">VET </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">が実施日・対応内容を入力して診療記録を登録する</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">記録が保存され一覧に表示される</t>
@@ -371,7 +1506,36 @@
     <t xml:space="preserve">TC-029</t>
   </si>
   <si>
-    <t xml:space="preserve">一般ユーザーが /app/consultations にアクセスする</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">一般ユーザーが </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/app/consultations </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">にアクセスする</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">アクセス拒否ページが表示される</t>
@@ -380,7 +1544,26 @@
     <t xml:space="preserve">TC-030</t>
   </si>
   <si>
-    <t xml:space="preserve">F-008 入力バリデーション</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F-008 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">入力バリデーション</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">全必須項目を満たしてフォームを送信する</t>
@@ -401,10 +1584,48 @@
     <t xml:space="preserve">TC-032</t>
   </si>
   <si>
-    <t xml:space="preserve">F-009 AI症状チェック</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Standard 以上のユーザーが症状種別・発症時期を入力して実行する</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F-009 AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">症状チェック</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Standard </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">以上のユーザーが症状種別・発症時期を入力して実行する</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">重症度と推奨対応が表示される</t>
@@ -413,7 +1634,26 @@
     <t xml:space="preserve">TC-033</t>
   </si>
   <si>
-    <t xml:space="preserve">Light プランのユーザーが症状チェックにアクセスする</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Light </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">プランのユーザーが症状チェックにアクセスする</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">アクセス制限エラーが表示される</t>
@@ -422,7 +1662,26 @@
     <t xml:space="preserve">TC-034</t>
   </si>
   <si>
-    <t xml:space="preserve">F-010 相談チャットボット</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F-010 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">相談チャットボット</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">症状を複数ターンにわたって入力する</t>
@@ -434,7 +1693,36 @@
     <t xml:space="preserve">TC-035</t>
   </si>
   <si>
-    <t xml:space="preserve">「2日間食べない」と入力する</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">日間食べない」と入力する</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">「今すぐ受診してください」即時受診案内が返答される</t>
@@ -443,7 +1731,26 @@
     <t xml:space="preserve">TC-036</t>
   </si>
   <si>
-    <t xml:space="preserve">F-011 カレンダー</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F-011 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">カレンダー</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">月次カレンダーを表示する</t>
@@ -455,7 +1762,36 @@
     <t xml:space="preserve">TC-037</t>
   </si>
   <si>
-    <t xml:space="preserve">同一ペット・同日に「診察」と「注射」の2種シールを追加する</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">同一ペット・同日に「診察」と「注射」の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">種シールを追加する</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">両方のシールが表示される</t>
@@ -473,7 +1809,26 @@
     <t xml:space="preserve">TC-039</t>
   </si>
   <si>
-    <t xml:space="preserve">VET ロールでカレンダーを開く</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">VET </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ロールでカレンダーを開く</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">全ユーザーの確定済み予約がサイドバーに表示される</t>
@@ -482,7 +1837,26 @@
     <t xml:space="preserve">TC-040</t>
   </si>
   <si>
-    <t xml:space="preserve">F-012 通知・リマインダー</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F-012 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">通知・リマインダー</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">予約が承認された後に通知一覧を開く</t>
@@ -503,7 +1877,26 @@
     <t xml:space="preserve">TC-042</t>
   </si>
   <si>
-    <t xml:space="preserve">F-013 サブスクリプション</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F-013 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">サブスクリプション</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">一般ユーザーでサブスクリプション画面を開く</t>
@@ -515,7 +1908,26 @@
     <t xml:space="preserve">TC-043</t>
   </si>
   <si>
-    <t xml:space="preserve">F-014 パスワード変更</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F-014 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">パスワード変更</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">現在パスワードを正しく入力して変更する</t>
@@ -539,7 +1951,46 @@
     <t xml:space="preserve">F-015 LINE Bot</t>
   </si>
   <si>
-    <t xml:space="preserve">LINE で Bot を友達追加する</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LINE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">で </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bot </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">を友達追加する</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">ウェルカムメッセージが自動返信される</t>
@@ -548,7 +1999,26 @@
     <t xml:space="preserve">TC-046</t>
   </si>
   <si>
-    <t xml:space="preserve">LINE Bot に症状メッセージを送信する</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LINE Bot </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">に症状メッセージを送信する</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">キーワードに応じた返答が届く</t>
@@ -560,16 +2030,93 @@
     <t xml:space="preserve">F-015 LINE Broadcast</t>
   </si>
   <si>
-    <t xml:space="preserve">ADMIN が LINE 一斉送信フォームからメッセージを送信する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bot フォロワー全員にメッセージが届く</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ADMIN </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">が </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LINE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">一斉送信フォームからメッセージを送信する</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bot </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">フォロワー全員にメッセージが届く</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">TC-048</t>
   </si>
   <si>
-    <t xml:space="preserve">LINE_CHANNEL_TOKEN 未設定の状態で一斉送信画面を開く</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LINE_CHANNEL_TOKEN </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">未設定の状態で一斉送信画面を開く</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">「チャンネルトークンが設定されていません」警告が表示され送信ボタンが無効になる</t>
@@ -581,7 +2128,66 @@
     <t xml:space="preserve">F-016 Slack Bot</t>
   </si>
   <si>
-    <t xml:space="preserve">Slack の DM で Bot に症状メッセージを送信する</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Slack </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">の </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">で </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bot </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">に症状メッセージを送信する</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">緊急度に応じた返答が届く</t>
@@ -590,28 +2196,172 @@
     <t xml:space="preserve">TC-050</t>
   </si>
   <si>
-    <t xml:space="preserve">F-017 Zoom オンライン診療</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Premium ユーザーがオンライン診療を予約する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">予約が登録され承認後に Zoom リンクが通知される</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F-017 Zoom </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">オンライン診療</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Premium </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ユーザーがオンライン診療を予約する</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">予約が登録され承認後に </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Zoom </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">リンクが通知される</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">TC-051</t>
   </si>
   <si>
-    <t xml:space="preserve">Standard ユーザーが /app/premium/online-care にアクセスする</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Standard </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ユーザーが </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/app/premium/online-care </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">にアクセスする</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">TC-052</t>
   </si>
   <si>
-    <t xml:space="preserve">F-018 予約枠管理</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADMIN が予約枠を登録する</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F-018 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">予約枠管理</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ADMIN </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">が予約枠を登録する</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">予約枠が保存され一般ユーザーのカレンダーに「空き」が表示される</t>
@@ -620,16 +2370,93 @@
     <t xml:space="preserve">TC-053</t>
   </si>
   <si>
-    <t xml:space="preserve">VET ロールで /app/admin/appointment-slots にアクセスする</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">VET </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ロールで </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/app/admin/appointment-slots </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">にアクセスする</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">TC-054</t>
   </si>
   <si>
-    <t xml:space="preserve">F-019 お知らせ管理</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADMIN がお知らせを作成・公開する</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F-019 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">お知らせ管理</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ADMIN </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">がお知らせを作成・公開する</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">お知らせが保存され一般ユーザーのダッシュボードに表示される</t>
@@ -638,16 +2465,75 @@
     <t xml:space="preserve">TC-055</t>
   </si>
   <si>
-    <t xml:space="preserve">F-021 サービス統計</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADMIN でサービス統計ページを開く</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F-021 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">サービス統計</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ADMIN </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">でサービス統計ページを開く</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">ユーザー数・ペット数・予約数等の集計値が表示される</t>
   </si>
   <si>
-    <t xml:space="preserve">機能ID</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">機能</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ID</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">機能名</t>
@@ -668,7 +2554,36 @@
     <t xml:space="preserve">ログイン認証</t>
   </si>
   <si>
-    <t xml:space="preserve">正常/異常ログイン、セッション発行</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">正常</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">異常ログイン、セッション発行</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">エラーメッセージ、入力表示</t>
@@ -680,16 +2595,142 @@
     <t xml:space="preserve">F-002</t>
   </si>
   <si>
-    <t xml:space="preserve">ダッシュボード（ロール別KPI）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KPI表示（管理/ユーザー別）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ウィジェット/レスポンシブ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">認可外データ非表示、XSS対策</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ダッシュボード（ロール別</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">KPI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">KPI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">表示（管理</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ユーザー別）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ウィジェット</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">レスポンシブ</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">認可外データ非表示、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">XSS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">対策</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">F-003</t>
@@ -698,10 +2739,78 @@
     <t xml:space="preserve">ユーザー管理</t>
   </si>
   <si>
-    <t xml:space="preserve">CRUD、重複メール制御</t>
-  </si>
-  <si>
-    <t xml:space="preserve">一覧/詳細/編集導線</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CRUD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">、重複メール制御</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">一覧</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">詳細</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">編集導線</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">権限制御、個人情報保護</t>
@@ -713,10 +2822,58 @@
     <t xml:space="preserve">ペット管理</t>
   </si>
   <si>
-    <t xml:space="preserve">CRUD、飼い主紐付け</t>
-  </si>
-  <si>
-    <t xml:space="preserve">一覧/フォーム操作</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CRUD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">、飼い主紐付け</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">一覧</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">フォーム操作</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">不正アクセス防止</t>
@@ -731,22 +2888,158 @@
     <t xml:space="preserve">登録更新削除、時系列整合</t>
   </si>
   <si>
-    <t xml:space="preserve">記録UI/表示</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ID改ざん耐性、入力検証</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">記録</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">UI/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">表示</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">改ざん耐性、入力検証</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">F-006</t>
   </si>
   <si>
-    <t xml:space="preserve">診療予約（申請/承認/却下/キャンセル）</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">診療予約（申請</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">承認</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">却下</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">キャンセル）</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">予約申請・承認・却下</t>
   </si>
   <si>
-    <t xml:space="preserve">カレンダーUI</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">カレンダー</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">UI</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">不正予約防止、権限チェック</t>
@@ -755,13 +3048,140 @@
     <t xml:space="preserve">F-007</t>
   </si>
   <si>
-    <t xml:space="preserve">診療記録 CRUD（VET/STAFF/ADMIN）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">履歴CRUD、添付紐付け</t>
-  </si>
-  <si>
-    <t xml:space="preserve">一覧/詳細/添付表示</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">診療記録 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CRUD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">VET/STAFF/ADMIN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">履歴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CRUD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">、添付紐付け</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">一覧</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">詳細</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">添付表示</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">添付検証、アクセス制御</t>
@@ -773,25 +3193,191 @@
     <t xml:space="preserve">入力バリデーション</t>
   </si>
   <si>
-    <t xml:space="preserve">必須/形式/範囲/重複</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">必須</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">形式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">範囲</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">重複</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">エラー表示統一</t>
   </si>
   <si>
-    <t xml:space="preserve">サーバ側検証、SQLi対策</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">サーバ側検証、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SQLi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">対策</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">F-009</t>
   </si>
   <si>
-    <t xml:space="preserve">AI症状チェック（OpenAI/フォールバック）</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">症状チェック（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">OpenAI/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">フォールバック）</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">入力→解析→推奨出力</t>
   </si>
   <si>
-    <t xml:space="preserve">結果表示/遷移</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">結果表示</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">遷移</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">プロンプト耐性、機微情報制御</t>
@@ -821,7 +3407,36 @@
     <t xml:space="preserve">月次カレンダー表示</t>
   </si>
   <si>
-    <t xml:space="preserve">手動/自動シールと予約表示</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">手動</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">自動シールと予約表示</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">同日複数種シールの表示</t>
@@ -833,7 +3448,36 @@
     <t xml:space="preserve">通知・スケジュールリマインダー</t>
   </si>
   <si>
-    <t xml:space="preserve">通知作成/既読管理</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">通知作成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">既読管理</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">未読・既読表示</t>
@@ -851,7 +3495,26 @@
     <t xml:space="preserve">契約プラン表示</t>
   </si>
   <si>
-    <t xml:space="preserve">プラン表示UI</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">プラン表示</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">UI</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">閲覧権限制御</t>
@@ -863,25 +3526,190 @@
     <t xml:space="preserve">パスワード変更</t>
   </si>
   <si>
-    <t xml:space="preserve">現在パスワード確認/更新</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">現在パスワード確認</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">更新</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">変更フォーム</t>
   </si>
   <si>
-    <t xml:space="preserve">認証エラー/更新完了</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">認証エラー</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">更新完了</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">F-015</t>
   </si>
   <si>
-    <t xml:space="preserve">LINE Bot（Webhook受信・返答・Broadcast送信）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Webhook受信・返答・一斉送信</t>
-  </si>
-  <si>
-    <t xml:space="preserve">友だち追加/メッセージ表示</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LINE Bot</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Webhook</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">受信・返答・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Broadcast</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">送信）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Webhook</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">受信・返答・一斉送信</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">友だち追加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">メッセージ表示</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">チャンネルトークン管理</t>
@@ -890,13 +3718,90 @@
     <t xml:space="preserve">F-016</t>
   </si>
   <si>
-    <t xml:space="preserve">Slack Bot（Webhook受信・返答）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Webhook受信・返答</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DM応答</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Slack Bot</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Webhook</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">受信・返答）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Webhook</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">受信・返答</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">応答</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">権限制御</t>
@@ -905,25 +3810,189 @@
     <t xml:space="preserve">F-017</t>
   </si>
   <si>
-    <t xml:space="preserve">Zoom オンライン診療（Premium）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">予約/リンク通知</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zoom遷移</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Premium制限</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Zoom </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">オンライン診療（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Premium</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">予約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">リンク通知</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Zoom</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">遷移</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Premium</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">制限</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">F-018</t>
   </si>
   <si>
-    <t xml:space="preserve">予約枠管理（ADMIN/STAFF）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">予約枠登録/空き表示</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">予約枠管理（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ADMIN/STAFF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">予約枠登録</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">空き表示</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">管理者・スタッフ限定</t>
@@ -932,7 +4001,36 @@
     <t xml:space="preserve">F-019</t>
   </si>
   <si>
-    <t xml:space="preserve">お知らせ管理（ADMIN/STAFF）</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">お知らせ管理（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ADMIN/STAFF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">作成・公開</t>
@@ -947,7 +4045,26 @@
     <t xml:space="preserve">ユーザー連携ステータスアイコン</t>
   </si>
   <si>
-    <t xml:space="preserve">LINE/Slack連携状態表示</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LINE/Slack</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">連携状態表示</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">編集フォーム上のチップ表示</t>
@@ -959,10 +4076,88 @@
     <t xml:space="preserve">F-021</t>
   </si>
   <si>
-    <t xml:space="preserve">サービス統計・DBバックアップ（ADMIN）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">統計集計/バックアップ</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">サービス統計・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">バックアップ（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ADMIN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">統計集計</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">バックアップ</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">管理画面表示</t>
@@ -971,7 +4166,39 @@
     <t xml:space="preserve">管理者限定</t>
   </si>
   <si>
-    <t xml:space="preserve">ブラウザ/デバイス</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ブラウザ</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">デバイス</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">バージョン</t>
@@ -986,7 +4213,46 @@
     <t xml:space="preserve">備考</t>
   </si>
   <si>
-    <t xml:space="preserve">Chrome（PC）</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Chrome</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">（最新版）</t>
@@ -998,13 +4264,110 @@
     <t xml:space="preserve">PC</t>
   </si>
   <si>
-    <t xml:space="preserve">Firefox（PC）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edge（PC）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chrome（スマートフォン）</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Firefox</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Edge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Chrome</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">（スマートフォン）</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">？</t>
@@ -1016,7 +4379,46 @@
     <t xml:space="preserve">iPhone</t>
   </si>
   <si>
-    <t xml:space="preserve">Safari（iPhone）</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Safari</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">iPhone</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1026,7 +4428,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1052,7 +4454,14 @@
     <font>
       <sz val="8"/>
       <color theme="1"/>
-      <name val="Microsoft Sans Serif"/>
+      <name val="游ゴシック体"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="8"/>
+      <name val="游ゴシック体"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -1064,10 +4473,40 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Microsoft Sans Serif"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="8"/>
       <color rgb="FFFFFFFF"/>
       <name val="Microsoft Sans Serif"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="8"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="游ゴシック体"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color theme="1"/>
+      <name val="游ゴシック体"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="游ゴシック体"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -1149,33 +4588,53 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1510,11 +4969,11 @@
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
@@ -1550,11 +5009,11 @@
       <c r="A8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -1588,27 +5047,28 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="9.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="41.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="30.7"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="6" style="1" width="8.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="38.99"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="6" style="6" width="8.45"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="1" width="8.45"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="8" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1619,932 +5079,950 @@
       <c r="B2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F2" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="21.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="21.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="C4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>29</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>33</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="4" t="s">
         <v>37</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>40</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>43</v>
       </c>
+      <c r="D8" s="5" t="s">
+        <v>44</v>
+      </c>
       <c r="E8" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>48</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>51</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11" s="4" t="s">
+      <c r="D11" s="5" t="s">
         <v>54</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>31</v>
+        <v>47</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E14" s="4" t="s">
         <v>63</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E15" s="4" t="s">
+      <c r="D15" s="5" t="s">
         <v>67</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C16" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E16" s="4" t="s">
+      <c r="D16" s="5" t="s">
         <v>70</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E17" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>73</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E18" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>76</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C19" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E19" s="4" t="s">
+      <c r="D19" s="5" t="s">
         <v>80</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="E20" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" s="5" t="s">
         <v>83</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E21" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" s="5" t="s">
         <v>86</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="C22" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E22" s="4" t="s">
         <v>90</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="C23" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E23" s="4" t="s">
         <v>93</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="C24" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E24" s="4" t="s">
         <v>96</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="C25" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E25" s="4" t="s">
         <v>99</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="E26" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" s="5" t="s">
         <v>102</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="E27" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D27" s="5" t="s">
         <v>105</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>31</v>
+        <v>89</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="E28" s="4" t="s">
         <v>108</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C29" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E29" s="4" t="s">
         <v>112</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="E30" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" s="5" t="s">
         <v>115</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="C31" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="E31" s="4" t="s">
+      <c r="D31" s="5" t="s">
         <v>119</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="E32" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D32" s="5" t="s">
         <v>122</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C33" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C33" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="E33" s="4" t="s">
         <v>126</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>24</v>
+        <v>125</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="E34" s="4" t="s">
         <v>129</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="C35" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C35" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D35" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="E35" s="4" t="s">
+      <c r="D35" s="5" t="s">
         <v>133</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="C36" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C36" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D36" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="E36" s="4" t="s">
+      <c r="D36" s="5" t="s">
         <v>136</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C37" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C37" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D37" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="E37" s="4" t="s">
+      <c r="D37" s="5" t="s">
         <v>140</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C38" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C38" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D38" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="E38" s="4" t="s">
+      <c r="D38" s="5" t="s">
         <v>143</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="E39" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D39" s="5" t="s">
         <v>146</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C40" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C40" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="E40" s="4" t="s">
         <v>149</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="C41" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C41" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="E41" s="4" t="s">
+      <c r="D41" s="5" t="s">
         <v>153</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="C42" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C42" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D42" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="E42" s="4" t="s">
+      <c r="D42" s="5" t="s">
         <v>156</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="C43" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C43" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D43" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="E43" s="4" t="s">
+      <c r="D43" s="5" t="s">
         <v>160</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="C44" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C44" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D44" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="E44" s="4" t="s">
+      <c r="D44" s="5" t="s">
         <v>164</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="E45" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D45" s="5" t="s">
         <v>167</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="C46" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C46" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="E46" s="4" t="s">
         <v>171</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="C47" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C47" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="E47" s="4" t="s">
         <v>174</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="C48" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C48" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>24</v>
+        <v>177</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="E49" s="4" t="s">
         <v>181</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="C50" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="C50" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="E50" s="4" t="s">
         <v>185</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="C51" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="C51" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="E51" s="4" t="s">
         <v>189</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>24</v>
+        <v>188</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="E52" s="4" t="s">
-        <v>129</v>
+        <v>192</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="C53" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C53" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="E53" s="4" t="s">
         <v>195</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>31</v>
+        <v>194</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="E54" s="4" t="s">
-        <v>115</v>
+        <v>198</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="C55" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C55" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="E55" s="4" t="s">
         <v>201</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="C56" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C56" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="E56" s="4" t="s">
         <v>205</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -2577,377 +6055,377 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="B1" s="6" t="s">
+      <c r="A1" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="B1" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="C1" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="D1" s="10" t="s">
         <v>210</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="B2" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>215</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="20.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="B3" s="4" t="s">
         <v>217</v>
       </c>
+      <c r="B3" s="5" t="s">
+        <v>218</v>
+      </c>
       <c r="C3" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="D3" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>220</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="B4" s="4" t="s">
         <v>222</v>
       </c>
+      <c r="B4" s="5" t="s">
+        <v>223</v>
+      </c>
       <c r="C4" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="D4" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>225</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="B5" s="4" t="s">
         <v>227</v>
       </c>
+      <c r="B5" s="5" t="s">
+        <v>228</v>
+      </c>
       <c r="C5" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="D5" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>230</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="B6" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>234</v>
       </c>
+      <c r="D6" s="5" t="s">
+        <v>235</v>
+      </c>
       <c r="E6" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="B7" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>240</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="B8" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>245</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="B9" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>250</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="C10" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>255</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="B11" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="D11" s="5" t="s">
         <v>260</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="B12" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="D12" s="5" t="s">
         <v>265</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="B13" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="C13" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="D13" s="5" t="s">
         <v>270</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="B14" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="D14" s="5" t="s">
         <v>275</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="B15" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="B15" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="C15" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="D15" s="5" t="s">
         <v>280</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="D16" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="D16" s="5" t="s">
         <v>285</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="E17" s="4" t="s">
         <v>290</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="C18" s="4" t="s">
         <v>293</v>
       </c>
+      <c r="C18" s="5" t="s">
+        <v>294</v>
+      </c>
       <c r="D18" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="B19" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="E19" s="4" t="s">
+      <c r="C19" s="5" t="s">
         <v>299</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="E20" s="5" t="s">
         <v>300</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="B21" s="4" t="s">
         <v>305</v>
       </c>
+      <c r="B21" s="5" t="s">
+        <v>306</v>
+      </c>
       <c r="C21" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="D21" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="D21" s="5" t="s">
         <v>308</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="B22" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="C22" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="D22" s="5" t="s">
         <v>313</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -2978,117 +6456,117 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="B1" s="6" t="s">
+      <c r="A1" s="10" t="s">
         <v>315</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="B1" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="C1" s="10" t="s">
         <v>317</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="D1" s="10" t="s">
         <v>318</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="20.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="B2" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>321</v>
       </c>
+      <c r="C2" s="5" t="s">
+        <v>322</v>
+      </c>
       <c r="D2" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="E2" s="1" t="s">
         <v>322</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="24.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="E3" s="11" t="s">
         <v>323</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="C4" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>321</v>
       </c>
+      <c r="C4" s="5" t="s">
+        <v>322</v>
+      </c>
       <c r="D4" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="E4" s="1" t="s">
         <v>322</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="25.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="C5" s="4" t="s">
         <v>326</v>
       </c>
+      <c r="B5" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>327</v>
+      </c>
       <c r="D5" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="E5" s="1" t="s">
         <v>327</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="25.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="C6" s="4"/>
-      <c r="E6" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="C6" s="5"/>
+      <c r="E6" s="11" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="28.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="E7" s="11" t="s">
         <v>329</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
